--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,38 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>3930fd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:13:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Add files via upload</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>a9cf6ff</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,38 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>a9cf6ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:15:36</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Remove duplicate comment for cart items</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7572f8c</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,9 +52,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,8 +421,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -545,6 +557,37 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>7572f8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46283.68477786391</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Refactor Excel update script for better clarity
+Refactor update_excel.py to improve argument handling and Excel file management.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0ac331d</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -52,10 +52,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -561,8 +562,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46283.68477786391</v>
+      <c r="A5" s="3" t="n">
+        <v>46283.6847778588</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -588,6 +589,37 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>0ac331d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46283.69043757788</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Add script to log changes in Excel file
+This script logs changes to an Excel file, capturing details such as user, branch, release, commit message, and commit ID.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3c6c8b0</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46283.69043757788</v>
+        <v>46283.69043758102</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -620,6 +620,36 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>3c6c8b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46283.69367683941</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Remove duplicate comment for cart items</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7ec46ee</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -625,7 +625,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46283.69367683941</v>
+        <v>46283.69367684028</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -650,6 +650,37 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>7ec46ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46283.53135293775</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Add timezone environment variable to workflow
+Added timezone environment variable for consistency.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2532b03</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -655,7 +655,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46283.53135293775</v>
+        <v>46283.53135293981</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -681,6 +681,36 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>2532b03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46283.65490851103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fix typo in CSS comment in _Layout.cshtml</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>89224b6</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46283.65490851103</v>
+        <v>46283.65490850694</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -711,6 +711,36 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>89224b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46284.91266907491</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fix formatting in Register.cshtml</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fe00c3f</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46284.91266907491</v>
+        <v>46284.91266907407</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -741,6 +741,37 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>fe00c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46290.99113628682</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Create README.md for FoodOrderSystem project
+Added a comprehensive README file for the FoodOrderSystem project, detailing features, installation instructions, and usage.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3b2bd94</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46290.99113628682</v>
+        <v>46290.99113628472</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -772,6 +772,36 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>3b2bd94</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46291.93226638783</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Update registrar_cambio.py</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ec80cd4</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46291.93226638783</v>
+        <v>46291.93226638889</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -802,6 +802,36 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>ec80cd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46293.59165377571</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Update README.md</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ba3c137</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -807,7 +807,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46293.59165377571</v>
+        <v>46293.59165377315</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -832,6 +832,36 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>ba3c137</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46296.71202640233</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Add section for Interrumped</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>76ba1b8</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -837,7 +837,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46296.71202640233</v>
+        <v>46296.71202640046</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -862,6 +862,36 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>76ba1b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46304.99705499826</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Update project description in README.md</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7d3ad4c</t>
         </is>
       </c>
     </row>

--- a/historial_cambios.xlsx
+++ b/historial_cambios.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -867,7 +867,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46304.99705499826</v>
+        <v>46304.997055</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -892,6 +892,36 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>7d3ad4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46306.9514929329</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GeanluisGL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Update README.md</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ed21c10</t>
         </is>
       </c>
     </row>
